--- a/db/A7XLK-1105-MarketAnalysis.xlsx
+++ b/db/A7XLK-1105-MarketAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258B8B8D-10BC-D94F-805F-3F6320C2009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5310DD4-24E2-EB42-9956-7A863743BC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34580" yWindow="1900" windowWidth="29760" windowHeight="13240" activeTab="1" xr2:uid="{D2AF3218-DF3A-914D-93E0-8410F12C8571}"/>
+    <workbookView xWindow="-32700" yWindow="620" windowWidth="29760" windowHeight="13240" xr2:uid="{D2AF3218-DF3A-914D-93E0-8410F12C8571}"/>
   </bookViews>
   <sheets>
     <sheet name="區域分析-01" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId3"/>
-    <pivotCache cacheId="14" r:id="rId4"/>
+    <pivotCache cacheId="15" r:id="rId3"/>
+    <pivotCache cacheId="16" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -265,7 +265,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="181" formatCode="#,##0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -328,7 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -467,19 +467,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -535,19 +523,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -603,19 +579,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -671,19 +635,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1593,6 +1545,9 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1649,6 +1604,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1705,6 +1663,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1761,6 +1722,9 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1817,6 +1781,9 @@
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3051,7 +3018,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -3107,7 +3074,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -3163,7 +3130,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -3219,7 +3186,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -3291,7 +3258,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -3413,7 +3380,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -3535,7 +3502,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -3657,7 +3624,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -5833,8 +5800,7 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5933,9 +5899,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:xForSave val="1"/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -5943,7 +5907,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5998,9 +5962,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:xForSave val="1"/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -6008,7 +5970,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -6063,9 +6025,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:xForSave val="1"/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -6073,7 +6033,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent4"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -9426,10 +9386,10 @@
       <xdr:rowOff>184150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9457,15 +9417,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9498,10 +9458,10 @@
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10323,7 +10283,185 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE5E1FF5-8F93-5D4B-8D53-2FA9409BDAE8}" name="樞紐分析表3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C933CB77-500D-0846-837D-B8F9FA10D073}" name="樞紐分析表1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="J10:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="37">
+        <item x="11"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="29"/>
+        <item x="8"/>
+        <item x="17"/>
+        <item x="26"/>
+        <item x="35"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="32"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="12"/>
+        <item x="30"/>
+        <item x="33"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="28"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="27"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="34"/>
+        <item x="25"/>
+        <item x="31"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 數字" fld="5" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE5E1FF5-8F93-5D4B-8D53-2FA9409BDAE8}" name="樞紐分析表3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H83:M88" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -10436,7 +10574,7 @@
     <pageField fld="3" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="平均值 - 數字" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
+    <dataField name="平均值 - 數字" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="177"/>
   </dataFields>
   <chartFormats count="8">
     <chartFormat chart="0" format="0" series="1">
@@ -10545,8 +10683,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACF04336-7B3D-A342-9990-49B490C95592}" name="樞紐分析表2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACF04336-7B3D-A342-9990-49B490C95592}" name="樞紐分析表2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="I49:M55" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0">
@@ -10768,347 +10906,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C933CB77-500D-0846-837D-B8F9FA10D073}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="J10:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="37">
-        <item x="11"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="29"/>
-        <item x="8"/>
-        <item x="17"/>
-        <item x="26"/>
-        <item x="35"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="32"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="33"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="28"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="27"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="34"/>
-        <item x="25"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 數字" fld="5" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E472707-6589-414B-B8AA-943FABDA29D1}" name="樞紐分析表5" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="I76:J81" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="33">
-        <item x="14"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="30"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="12"/>
-        <item x="21"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="26"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="27"/>
-        <item x="0"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="加總 - 數字" fld="5" baseField="0" baseItem="0" numFmtId="181"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D0F693C-7021-BC44-94FB-78B7F3E25852}" name="樞紐分析表4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D0F693C-7021-BC44-94FB-78B7F3E25852}" name="樞紐分析表4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="J37:O43" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0" sortType="descending">
@@ -11476,6 +11275,167 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E472707-6589-414B-B8AA-943FABDA29D1}" name="樞紐分析表5" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="I76:J81" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="33">
+        <item x="14"/>
+        <item x="6"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="30"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="26"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="27"/>
+        <item x="0"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="加總 - 數字" fld="5" baseField="0" baseItem="0" numFmtId="177"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>

--- a/db/A7XLK-1105-MarketAnalysis.xlsx
+++ b/db/A7XLK-1105-MarketAnalysis.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5310DD4-24E2-EB42-9956-7A863743BC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496FDBFC-7E16-EB42-AEC8-37AF476C0B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32700" yWindow="620" windowWidth="29760" windowHeight="13240" xr2:uid="{D2AF3218-DF3A-914D-93E0-8410F12C8571}"/>
+    <workbookView xWindow="240" yWindow="720" windowWidth="27420" windowHeight="17060" activeTab="2" xr2:uid="{D2AF3218-DF3A-914D-93E0-8410F12C8571}"/>
   </bookViews>
   <sheets>
     <sheet name="區域分析-01" sheetId="1" r:id="rId1"/>
     <sheet name="區域分析-02" sheetId="2" r:id="rId2"/>
+    <sheet name="區域分析-03" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId3"/>
-    <pivotCache cacheId="16" r:id="rId4"/>
+    <pivotCache cacheId="17" r:id="rId4"/>
+    <pivotCache cacheId="18" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="75">
   <si>
     <t xml:space="preserve">內政部 2021 預售屋 住宅 實價登錄資料 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -258,6 +259,64 @@
     <t>第四季只有 10-11兩個月資料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.facebook.com/groups/1951117865015671/permalink/4522509421209823/</t>
+  </si>
+  <si>
+    <t>2021/11 龜山區實價登錄分布,</t>
+  </si>
+  <si>
+    <t>區域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021/10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,500萬以上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,200-1,500萬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,000-1,200萬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,000萬以下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021/11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰山區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新莊區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -267,7 +326,7 @@
     <numFmt numFmtId="176" formatCode="#,##0.0_ "/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -282,6 +341,12 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF050505"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -306,7 +371,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -338,6 +403,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9416,16 +9487,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10283,7 +10354,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C933CB77-500D-0846-837D-B8F9FA10D073}" name="樞紐分析表1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C933CB77-500D-0846-837D-B8F9FA10D073}" name="樞紐分析表1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="J10:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -10461,7 +10532,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE5E1FF5-8F93-5D4B-8D53-2FA9409BDAE8}" name="樞紐分析表3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE5E1FF5-8F93-5D4B-8D53-2FA9409BDAE8}" name="樞紐分析表3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H83:M88" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -10684,7 +10755,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACF04336-7B3D-A342-9990-49B490C95592}" name="樞紐分析表2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACF04336-7B3D-A342-9990-49B490C95592}" name="樞紐分析表2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="I49:M55" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0">
@@ -10907,7 +10978,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D0F693C-7021-BC44-94FB-78B7F3E25852}" name="樞紐分析表4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D0F693C-7021-BC44-94FB-78B7F3E25852}" name="樞紐分析表4" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="J37:O43" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0" sortType="descending">
@@ -11276,7 +11347,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E472707-6589-414B-B8AA-943FABDA29D1}" name="樞紐分析表5" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E472707-6589-414B-B8AA-943FABDA29D1}" name="樞紐分析表5" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="I76:J81" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -13777,4 +13848,1115 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA92196-98A7-9F43-9F6D-B6A0BC8691EE}">
+  <dimension ref="C3:G210"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:7">
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7">
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7">
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3">
+        <v>44561</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" ht="19">
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7">
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7">
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7">
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7">
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7">
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7">
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7">
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7">
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7">
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7">
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7">
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7">
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7">
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7">
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7">
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7">
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7">
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7">
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7">
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7">
+      <c r="C29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:7">
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="3:7">
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="3:7">
+      <c r="C32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7">
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7">
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7">
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7">
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7">
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7">
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7">
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" t="s">
+        <v>48</v>
+      </c>
+      <c r="G39">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7">
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" t="s">
+        <v>48</v>
+      </c>
+      <c r="G40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7">
+      <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="3:7">
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" t="s">
+        <v>48</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7">
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" spans="3:7">
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="3:7">
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="3:7">
+      <c r="D46" s="12"/>
+    </row>
+    <row r="47" spans="3:7">
+      <c r="D47" s="12"/>
+    </row>
+    <row r="48" spans="3:7">
+      <c r="D48" s="12"/>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" s="12"/>
+    </row>
+    <row r="50" spans="4:4">
+      <c r="D50" s="12"/>
+    </row>
+    <row r="51" spans="4:4">
+      <c r="D51" s="12"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="12"/>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" s="12"/>
+    </row>
+    <row r="55" spans="4:4">
+      <c r="D55" s="12"/>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="12"/>
+    </row>
+    <row r="57" spans="4:4">
+      <c r="D57" s="12"/>
+    </row>
+    <row r="58" spans="4:4">
+      <c r="D58" s="12"/>
+    </row>
+    <row r="59" spans="4:4">
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" spans="4:4">
+      <c r="D60" s="12"/>
+    </row>
+    <row r="61" spans="4:4">
+      <c r="D61" s="12"/>
+    </row>
+    <row r="62" spans="4:4">
+      <c r="D62" s="12"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="12"/>
+    </row>
+    <row r="64" spans="4:4">
+      <c r="D64" s="12"/>
+    </row>
+    <row r="65" spans="4:4">
+      <c r="D65" s="12"/>
+    </row>
+    <row r="66" spans="4:4">
+      <c r="D66" s="12"/>
+    </row>
+    <row r="67" spans="4:4">
+      <c r="D67" s="12"/>
+    </row>
+    <row r="68" spans="4:4">
+      <c r="D68" s="12"/>
+    </row>
+    <row r="69" spans="4:4">
+      <c r="D69" s="12"/>
+    </row>
+    <row r="70" spans="4:4">
+      <c r="D70" s="12"/>
+    </row>
+    <row r="71" spans="4:4">
+      <c r="D71" s="12"/>
+    </row>
+    <row r="72" spans="4:4">
+      <c r="D72" s="12"/>
+    </row>
+    <row r="73" spans="4:4">
+      <c r="D73" s="12"/>
+    </row>
+    <row r="74" spans="4:4">
+      <c r="D74" s="12"/>
+    </row>
+    <row r="75" spans="4:4">
+      <c r="D75" s="12"/>
+    </row>
+    <row r="76" spans="4:4">
+      <c r="D76" s="12"/>
+    </row>
+    <row r="77" spans="4:4">
+      <c r="D77" s="12"/>
+    </row>
+    <row r="78" spans="4:4">
+      <c r="D78" s="12"/>
+    </row>
+    <row r="79" spans="4:4">
+      <c r="D79" s="12"/>
+    </row>
+    <row r="80" spans="4:4">
+      <c r="D80" s="12"/>
+    </row>
+    <row r="81" spans="4:4">
+      <c r="D81" s="12"/>
+    </row>
+    <row r="82" spans="4:4">
+      <c r="D82" s="12"/>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="12"/>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="12"/>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="12"/>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="12"/>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="12"/>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="12"/>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="12"/>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="12"/>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="12"/>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="12"/>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="12"/>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="12"/>
+    </row>
+    <row r="95" spans="4:4">
+      <c r="D95" s="12"/>
+    </row>
+    <row r="96" spans="4:4">
+      <c r="D96" s="12"/>
+    </row>
+    <row r="97" spans="4:4">
+      <c r="D97" s="12"/>
+    </row>
+    <row r="98" spans="4:4">
+      <c r="D98" s="12"/>
+    </row>
+    <row r="99" spans="4:4">
+      <c r="D99" s="12"/>
+    </row>
+    <row r="100" spans="4:4">
+      <c r="D100" s="12"/>
+    </row>
+    <row r="101" spans="4:4">
+      <c r="D101" s="12"/>
+    </row>
+    <row r="102" spans="4:4">
+      <c r="D102" s="12"/>
+    </row>
+    <row r="103" spans="4:4">
+      <c r="D103" s="12"/>
+    </row>
+    <row r="104" spans="4:4">
+      <c r="D104" s="12"/>
+    </row>
+    <row r="105" spans="4:4">
+      <c r="D105" s="12"/>
+    </row>
+    <row r="106" spans="4:4">
+      <c r="D106" s="12"/>
+    </row>
+    <row r="107" spans="4:4">
+      <c r="D107" s="12"/>
+    </row>
+    <row r="108" spans="4:4">
+      <c r="D108" s="12"/>
+    </row>
+    <row r="109" spans="4:4">
+      <c r="D109" s="12"/>
+    </row>
+    <row r="110" spans="4:4">
+      <c r="D110" s="12"/>
+    </row>
+    <row r="111" spans="4:4">
+      <c r="D111" s="12"/>
+    </row>
+    <row r="112" spans="4:4">
+      <c r="D112" s="12"/>
+    </row>
+    <row r="113" spans="4:4">
+      <c r="D113" s="12"/>
+    </row>
+    <row r="114" spans="4:4">
+      <c r="D114" s="12"/>
+    </row>
+    <row r="115" spans="4:4">
+      <c r="D115" s="12"/>
+    </row>
+    <row r="116" spans="4:4">
+      <c r="D116" s="12"/>
+    </row>
+    <row r="117" spans="4:4">
+      <c r="D117" s="12"/>
+    </row>
+    <row r="118" spans="4:4">
+      <c r="D118" s="12"/>
+    </row>
+    <row r="119" spans="4:4">
+      <c r="D119" s="12"/>
+    </row>
+    <row r="120" spans="4:4">
+      <c r="D120" s="12"/>
+    </row>
+    <row r="121" spans="4:4">
+      <c r="D121" s="12"/>
+    </row>
+    <row r="122" spans="4:4">
+      <c r="D122" s="12"/>
+    </row>
+    <row r="123" spans="4:4">
+      <c r="D123" s="12"/>
+    </row>
+    <row r="124" spans="4:4">
+      <c r="D124" s="12"/>
+    </row>
+    <row r="125" spans="4:4">
+      <c r="D125" s="12"/>
+    </row>
+    <row r="126" spans="4:4">
+      <c r="D126" s="12"/>
+    </row>
+    <row r="127" spans="4:4">
+      <c r="D127" s="12"/>
+    </row>
+    <row r="128" spans="4:4">
+      <c r="D128" s="12"/>
+    </row>
+    <row r="129" spans="4:4">
+      <c r="D129" s="12"/>
+    </row>
+    <row r="130" spans="4:4">
+      <c r="D130" s="12"/>
+    </row>
+    <row r="131" spans="4:4">
+      <c r="D131" s="12"/>
+    </row>
+    <row r="132" spans="4:4">
+      <c r="D132" s="12"/>
+    </row>
+    <row r="133" spans="4:4">
+      <c r="D133" s="12"/>
+    </row>
+    <row r="134" spans="4:4">
+      <c r="D134" s="12"/>
+    </row>
+    <row r="135" spans="4:4">
+      <c r="D135" s="12"/>
+    </row>
+    <row r="136" spans="4:4">
+      <c r="D136" s="12"/>
+    </row>
+    <row r="137" spans="4:4">
+      <c r="D137" s="12"/>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" s="12"/>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" s="12"/>
+    </row>
+    <row r="140" spans="4:4">
+      <c r="D140" s="12"/>
+    </row>
+    <row r="141" spans="4:4">
+      <c r="D141" s="12"/>
+    </row>
+    <row r="142" spans="4:4">
+      <c r="D142" s="12"/>
+    </row>
+    <row r="143" spans="4:4">
+      <c r="D143" s="12"/>
+    </row>
+    <row r="144" spans="4:4">
+      <c r="D144" s="12"/>
+    </row>
+    <row r="145" spans="4:4">
+      <c r="D145" s="12"/>
+    </row>
+    <row r="146" spans="4:4">
+      <c r="D146" s="12"/>
+    </row>
+    <row r="147" spans="4:4">
+      <c r="D147" s="12"/>
+    </row>
+    <row r="148" spans="4:4">
+      <c r="D148" s="12"/>
+    </row>
+    <row r="149" spans="4:4">
+      <c r="D149" s="12"/>
+    </row>
+    <row r="150" spans="4:4">
+      <c r="D150" s="12"/>
+    </row>
+    <row r="151" spans="4:4">
+      <c r="D151" s="12"/>
+    </row>
+    <row r="152" spans="4:4">
+      <c r="D152" s="12"/>
+    </row>
+    <row r="153" spans="4:4">
+      <c r="D153" s="12"/>
+    </row>
+    <row r="154" spans="4:4">
+      <c r="D154" s="12"/>
+    </row>
+    <row r="155" spans="4:4">
+      <c r="D155" s="12"/>
+    </row>
+    <row r="156" spans="4:4">
+      <c r="D156" s="12"/>
+    </row>
+    <row r="157" spans="4:4">
+      <c r="D157" s="12"/>
+    </row>
+    <row r="158" spans="4:4">
+      <c r="D158" s="12"/>
+    </row>
+    <row r="159" spans="4:4">
+      <c r="D159" s="12"/>
+    </row>
+    <row r="160" spans="4:4">
+      <c r="D160" s="12"/>
+    </row>
+    <row r="161" spans="4:4">
+      <c r="D161" s="12"/>
+    </row>
+    <row r="162" spans="4:4">
+      <c r="D162" s="12"/>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" s="12"/>
+    </row>
+    <row r="164" spans="4:4">
+      <c r="D164" s="12"/>
+    </row>
+    <row r="165" spans="4:4">
+      <c r="D165" s="12"/>
+    </row>
+    <row r="166" spans="4:4">
+      <c r="D166" s="12"/>
+    </row>
+    <row r="167" spans="4:4">
+      <c r="D167" s="12"/>
+    </row>
+    <row r="168" spans="4:4">
+      <c r="D168" s="12"/>
+    </row>
+    <row r="169" spans="4:4">
+      <c r="D169" s="12"/>
+    </row>
+    <row r="170" spans="4:4">
+      <c r="D170" s="12"/>
+    </row>
+    <row r="171" spans="4:4">
+      <c r="D171" s="12"/>
+    </row>
+    <row r="172" spans="4:4">
+      <c r="D172" s="12"/>
+    </row>
+    <row r="173" spans="4:4">
+      <c r="D173" s="12"/>
+    </row>
+    <row r="174" spans="4:4">
+      <c r="D174" s="12"/>
+    </row>
+    <row r="175" spans="4:4">
+      <c r="D175" s="12"/>
+    </row>
+    <row r="176" spans="4:4">
+      <c r="D176" s="12"/>
+    </row>
+    <row r="177" spans="4:4">
+      <c r="D177" s="12"/>
+    </row>
+    <row r="178" spans="4:4">
+      <c r="D178" s="12"/>
+    </row>
+    <row r="179" spans="4:4">
+      <c r="D179" s="12"/>
+    </row>
+    <row r="180" spans="4:4">
+      <c r="D180" s="12"/>
+    </row>
+    <row r="181" spans="4:4">
+      <c r="D181" s="12"/>
+    </row>
+    <row r="182" spans="4:4">
+      <c r="D182" s="12"/>
+    </row>
+    <row r="183" spans="4:4">
+      <c r="D183" s="12"/>
+    </row>
+    <row r="184" spans="4:4">
+      <c r="D184" s="12"/>
+    </row>
+    <row r="185" spans="4:4">
+      <c r="D185" s="12"/>
+    </row>
+    <row r="186" spans="4:4">
+      <c r="D186" s="12"/>
+    </row>
+    <row r="187" spans="4:4">
+      <c r="D187" s="12"/>
+    </row>
+    <row r="188" spans="4:4">
+      <c r="D188" s="12"/>
+    </row>
+    <row r="189" spans="4:4">
+      <c r="D189" s="12"/>
+    </row>
+    <row r="190" spans="4:4">
+      <c r="D190" s="12"/>
+    </row>
+    <row r="191" spans="4:4">
+      <c r="D191" s="12"/>
+    </row>
+    <row r="192" spans="4:4">
+      <c r="D192" s="12"/>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" s="12"/>
+    </row>
+    <row r="194" spans="4:4">
+      <c r="D194" s="12"/>
+    </row>
+    <row r="195" spans="4:4">
+      <c r="D195" s="12"/>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" s="12"/>
+    </row>
+    <row r="197" spans="4:4">
+      <c r="D197" s="12"/>
+    </row>
+    <row r="198" spans="4:4">
+      <c r="D198" s="12"/>
+    </row>
+    <row r="199" spans="4:4">
+      <c r="D199" s="12"/>
+    </row>
+    <row r="200" spans="4:4">
+      <c r="D200" s="12"/>
+    </row>
+    <row r="201" spans="4:4">
+      <c r="D201" s="12"/>
+    </row>
+    <row r="202" spans="4:4">
+      <c r="D202" s="12"/>
+    </row>
+    <row r="203" spans="4:4">
+      <c r="D203" s="12"/>
+    </row>
+    <row r="204" spans="4:4">
+      <c r="D204" s="12"/>
+    </row>
+    <row r="205" spans="4:4">
+      <c r="D205" s="12"/>
+    </row>
+    <row r="206" spans="4:4">
+      <c r="D206" s="12"/>
+    </row>
+    <row r="207" spans="4:4">
+      <c r="D207" s="12"/>
+    </row>
+    <row r="208" spans="4:4">
+      <c r="D208" s="12"/>
+    </row>
+    <row r="209" spans="4:4">
+      <c r="D209" s="12"/>
+    </row>
+    <row r="210" spans="4:4">
+      <c r="D210" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/db/A7XLK-1105-MarketAnalysis.xlsx
+++ b/db/A7XLK-1105-MarketAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496FDBFC-7E16-EB42-AEC8-37AF476C0B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74ED32E2-2909-9842-9D30-8E15C28DE15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="720" windowWidth="27420" windowHeight="17060" activeTab="2" xr2:uid="{D2AF3218-DF3A-914D-93E0-8410F12C8571}"/>
+    <workbookView xWindow="4260" yWindow="940" windowWidth="27420" windowHeight="17060" activeTab="2" xr2:uid="{D2AF3218-DF3A-914D-93E0-8410F12C8571}"/>
   </bookViews>
   <sheets>
     <sheet name="區域分析-01" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,10 @@
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId4"/>
-    <pivotCache cacheId="18" r:id="rId5"/>
+    <pivotCache cacheId="39" r:id="rId4"/>
+    <pivotCache cacheId="32" r:id="rId5"/>
+    <pivotCache cacheId="37" r:id="rId6"/>
+    <pivotCache cacheId="45" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="87">
   <si>
     <t xml:space="preserve">內政部 2021 預售屋 住宅 實價登錄資料 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -271,11 +273,20 @@
   </si>
   <si>
     <t>時間</t>
+  </si>
+  <si>
+    <t>時間</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>類型</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>單位</t>
+  </si>
+  <si>
+    <t>龜山區</t>
   </si>
   <si>
     <t>龜山區</t>
@@ -286,24 +297,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,500萬以上</t>
+    <t>2021/11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,200-1,500萬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,000-1,200萬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,000萬以下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021/11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>泰山區</t>
   </si>
   <si>
     <t>泰山區</t>
@@ -311,11 +309,51 @@
   </si>
   <si>
     <t>林口區</t>
+  </si>
+  <si>
+    <t>林口區</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>新莊區</t>
+  </si>
+  <si>
+    <t>新莊區</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 1,000-1,200萬</t>
+  </si>
+  <si>
+    <t>3. 1,000-1,200萬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 1,500萬以上</t>
+  </si>
+  <si>
+    <t>1. 1,500萬以上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 1,200-1,500萬</t>
+  </si>
+  <si>
+    <t>2. 1,200-1,500萬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 1,000萬以下</t>
+  </si>
+  <si>
+    <t>4. 1,000萬以下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(全部)</t>
+  </si>
+  <si>
+    <t>比例</t>
   </si>
 </sst>
 </file>
@@ -6711,6 +6749,3377 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-1105-MarketAnalysis.xlsx]區域分析-03!樞紐分析表6</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800"/>
+              <a:t>2021/10-11 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" sz="1800"/>
+              <a:t>區域實價登錄 房價區間 戶數 分析</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$K$10:$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>林口區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$J$12:$J$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$K$12:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F194-7043-9935-417903C1311C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$L$10:$L$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>泰山區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$J$12:$J$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$L$12:$L$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000041-F194-7043-9935-417903C1311C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$M$10:$M$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>新莊區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$J$12:$J$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$M$12:$M$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000042-F194-7043-9935-417903C1311C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$N$10:$N$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>龜山區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$J$12:$J$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$N$12:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000043-F194-7043-9935-417903C1311C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="537271279"/>
+        <c:axId val="12795728"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="537271279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="12795728"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="12795728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-TW" altLang="en-US" sz="1200"/>
+                  <a:t>實價登錄戶數</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="537271279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+          <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-1105-MarketAnalysis.xlsx]區域分析-03!樞紐分析表7</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800"/>
+              <a:t>2021/10-11 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" sz="1800"/>
+              <a:t>區域實價登錄   房價區間 佔比 分析</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$J$48:$J$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>林口區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$I$50:$I$54</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$J$50:$J$54</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.43254999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30359999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1132</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15065000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-60A7-FD43-BE9D-E0BD95996F38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$K$48:$K$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>泰山區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$I$50:$I$54</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$K$50:$K$54</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.442</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.23810000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26629999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.355E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-60A7-FD43-BE9D-E0BD95996F38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$L$48:$L$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>新莊區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$I$50:$I$54</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$L$50:$L$54</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.73934999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11845</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11365</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8549999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-60A7-FD43-BE9D-E0BD95996F38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'區域分析-03'!$M$48:$M$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>龜山區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'區域分析-03'!$I$50:$I$54</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1. 1,500萬以上</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. 1,200-1,500萬</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. 1,000-1,200萬</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. 1,000萬以下</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'區域分析-03'!$M$50:$M$54</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.5649999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27290000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.23659999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.41485</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-60A7-FD43-BE9D-E0BD95996F38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="420934287"/>
+        <c:axId val="420935935"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="420934287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="420935935"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="420935935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-TW" altLang="en-US" sz="1200"/>
+                  <a:t>實價登錄展比</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="420934287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+          <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -6872,6 +10281,86 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9447,6 +12936,1014 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -9637,8 +14134,180 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>774700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{855AA69B-0631-894E-89C6-F5FE9FB107C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B912E9D4-0E2F-E74E-A450-5CD3548B842A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44573.393430787037" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="36" xr:uid="{6AC9C039-C392-744F-9456-45BFA85F67F0}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44573.920329050925" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="32" xr:uid="{44C0C241-6EEA-B841-BB72-CBF1F0D98C4C}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="C10:G42" sheet="區域分析-03"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="區域" numFmtId="0">
+      <sharedItems count="4">
+        <s v="龜山區"/>
+        <s v="泰山區"/>
+        <s v="林口區"/>
+        <s v="新莊區"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="時間" numFmtId="49">
+      <sharedItems count="2">
+        <s v="2021/10"/>
+        <s v="2021/11"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="類型" numFmtId="0">
+      <sharedItems count="8">
+        <s v="1. 1,500萬以上"/>
+        <s v="2. 1,200-1,500萬"/>
+        <s v="3. 1,000-1,200萬"/>
+        <s v="4. 1,000萬以下"/>
+        <s v="1,000-1,200萬" u="1"/>
+        <s v="1,500萬以上" u="1"/>
+        <s v="1,200-1,500萬" u="1"/>
+        <s v="1,000萬以下" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="單位" numFmtId="0">
+      <sharedItems count="1">
+        <s v="戶數"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="數字" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="213"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44573.920329166664" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="32" xr:uid="{C72E47A0-7A73-374E-B7B4-EE7010D22CCA}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B37:G69" sheet="區域分析-02"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="房型" numFmtId="0">
+      <sharedItems count="4">
+        <s v="2房"/>
+        <s v="3房"/>
+        <s v="4房"/>
+        <s v="其他"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="年份" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2021" maxValue="2021"/>
+    </cacheField>
+    <cacheField name="季度" numFmtId="0">
+      <sharedItems count="4">
+        <s v="第一季"/>
+        <s v="第二季"/>
+        <s v="第三季"/>
+        <s v="第四季"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="類別" numFmtId="0">
+      <sharedItems count="2">
+        <s v="成交數"/>
+        <s v="比例"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="單位" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="數字" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.3099999999999999E-2" maxValue="513"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44573.92032928241" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="36" xr:uid="{6AC9C039-C392-744F-9456-45BFA85F67F0}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B10:G46" sheet="區域分析-01"/>
   </cacheSource>
@@ -9672,44 +14341,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="數字" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="26.7" maxValue="1469" count="36">
-        <n v="857"/>
-        <n v="965"/>
-        <n v="27.1"/>
-        <n v="64"/>
-        <n v="1328"/>
-        <n v="39.4"/>
-        <n v="404"/>
-        <n v="1359"/>
-        <n v="35.299999999999997"/>
-        <n v="911"/>
-        <n v="1008"/>
-        <n v="26.7"/>
-        <n v="73"/>
-        <n v="1360"/>
-        <n v="40.1"/>
-        <n v="317"/>
-        <n v="1275"/>
-        <n v="36"/>
-        <n v="1064"/>
-        <n v="1053"/>
-        <n v="27.8"/>
-        <n v="51"/>
-        <n v="1382"/>
-        <n v="41.2"/>
-        <n v="398"/>
-        <n v="1425"/>
-        <n v="38"/>
-        <n v="1174"/>
-        <n v="1048"/>
-        <n v="29.1"/>
-        <n v="122"/>
-        <n v="1469"/>
-        <n v="43.4"/>
-        <n v="199"/>
-        <n v="1422"/>
-        <n v="38.9"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="26.7" maxValue="1469"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -9720,74 +14352,95 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44573.448268287037" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="32" xr:uid="{C72E47A0-7A73-374E-B7B4-EE7010D22CCA}">
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44573.928463078701" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="64" xr:uid="{15737959-7BEE-3443-9A6C-73975CB9E449}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B37:G69" sheet="區域分析-02"/>
+    <worksheetSource ref="C10:G74" sheet="區域分析-03"/>
   </cacheSource>
-  <cacheFields count="6">
-    <cacheField name="房型" numFmtId="0">
+  <cacheFields count="5">
+    <cacheField name="區域" numFmtId="0">
       <sharedItems count="4">
-        <s v="2房"/>
-        <s v="3房"/>
-        <s v="4房"/>
-        <s v="其他"/>
+        <s v="龜山區"/>
+        <s v="泰山區"/>
+        <s v="林口區"/>
+        <s v="新莊區"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="年份" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2021" maxValue="2021"/>
+    <cacheField name="時間" numFmtId="49">
+      <sharedItems/>
     </cacheField>
-    <cacheField name="季度" numFmtId="0">
+    <cacheField name="類型" numFmtId="0">
       <sharedItems count="4">
-        <s v="第一季"/>
-        <s v="第二季"/>
-        <s v="第三季"/>
-        <s v="第四季"/>
+        <s v="1. 1,500萬以上"/>
+        <s v="2. 1,200-1,500萬"/>
+        <s v="3. 1,000-1,200萬"/>
+        <s v="4. 1,000萬以下"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="類別" numFmtId="0">
+    <cacheField name="單位" numFmtId="0">
       <sharedItems count="2">
-        <s v="成交數"/>
+        <s v="戶數"/>
         <s v="比例"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="單位" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
     <cacheField name="數字" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.3099999999999999E-2" maxValue="513" count="32">
-        <n v="303"/>
-        <n v="419"/>
-        <n v="22"/>
-        <n v="113"/>
-        <n v="0.35360000000000003"/>
-        <n v="0.4889"/>
-        <n v="2.5700000000000001E-2"/>
-        <n v="0.13189999999999999"/>
-        <n v="415"/>
-        <n v="442"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.7100000000000001E-2" maxValue="213" count="56">
+        <n v="27"/>
+        <n v="142"/>
+        <n v="124"/>
+        <n v="187"/>
+        <n v="46"/>
+        <n v="121"/>
+        <n v="104"/>
+        <n v="213"/>
+        <n v="31"/>
+        <n v="17"/>
         <n v="21"/>
-        <n v="33"/>
-        <n v="0.45550000000000002"/>
-        <n v="0.48520000000000002"/>
-        <n v="2.3099999999999999E-2"/>
-        <n v="3.6200000000000003E-2"/>
-        <n v="513"/>
-        <n v="492"/>
-        <n v="31"/>
-        <n v="28"/>
-        <n v="0.48209999999999997"/>
-        <n v="0.46239999999999998"/>
-        <n v="2.9100000000000001E-2"/>
-        <n v="2.63E-2"/>
-        <n v="330"/>
-        <n v="367"/>
-        <n v="26"/>
-        <n v="161"/>
-        <n v="0.37330000000000002"/>
-        <n v="0.41520000000000001"/>
-        <n v="2.9399999999999999E-2"/>
-        <n v="0.18210000000000001"/>
+        <n v="2"/>
+        <n v="9"/>
+        <n v="3"/>
+        <n v="40"/>
+        <n v="41"/>
+        <n v="8"/>
+        <n v="24"/>
+        <n v="23"/>
+        <n v="11"/>
+        <n v="7"/>
+        <n v="4"/>
+        <n v="95"/>
+        <n v="50"/>
+        <n v="12"/>
+        <n v="10"/>
+        <n v="5.6300000000000003E-2"/>
+        <n v="0.29580000000000001"/>
+        <n v="0.25829999999999997"/>
+        <n v="0.3896"/>
+        <n v="9.5000000000000001E-2"/>
+        <n v="0.25"/>
+        <n v="0.21490000000000001"/>
+        <n v="0.44009999999999999"/>
+        <n v="0.43659999999999999"/>
+        <n v="0.2394"/>
+        <n v="2.8199999999999999E-2"/>
+        <n v="0.44740000000000002"/>
+        <n v="0.23680000000000001"/>
+        <n v="7.8899999999999998E-2"/>
+        <n v="0.35399999999999998"/>
+        <n v="0.36280000000000001"/>
+        <n v="7.0800000000000002E-2"/>
+        <n v="0.21240000000000001"/>
+        <n v="0.5111"/>
+        <n v="0.24440000000000001"/>
+        <n v="0.15559999999999999"/>
+        <n v="8.8900000000000007E-2"/>
+        <n v="0.81200000000000006"/>
+        <n v="7.6899999999999996E-2"/>
+        <n v="9.4E-2"/>
+        <n v="1.7100000000000001E-2"/>
+        <n v="0.66669999999999996"/>
+        <n v="0.16"/>
+        <n v="0.1333"/>
+        <n v="0.04"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -9800,294 +14453,230 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="36">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="32">
   <r>
     <x v="0"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="筆"/>
     <x v="0"/>
+    <n v="27"/>
   </r>
   <r>
     <x v="0"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="萬元"/>
-    <x v="1"/>
+    <x v="0"/>
+    <n v="142"/>
   </r>
   <r>
     <x v="0"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="萬元"/>
+    <x v="0"/>
+    <n v="124"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="187"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="121"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
     <x v="2"/>
+    <x v="0"/>
+    <n v="104"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="213"/>
   </r>
   <r>
     <x v="1"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="筆"/>
-    <x v="3"/>
+    <x v="0"/>
+    <n v="31"/>
   </r>
   <r>
     <x v="1"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="萬元"/>
-    <x v="4"/>
+    <x v="0"/>
+    <n v="17"/>
   </r>
   <r>
     <x v="1"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="萬元"/>
-    <x v="5"/>
+    <x v="0"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="3"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="筆"/>
-    <x v="6"/>
+    <x v="0"/>
+    <n v="40"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="萬元"/>
-    <x v="7"/>
+    <x v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="萬元"/>
-    <x v="8"/>
-  </r>
-  <r>
     <x v="0"/>
-    <n v="2021"/>
-    <x v="1"/>
-    <x v="0"/>
-    <s v="筆"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <n v="2021"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <n v="2021"/>
-    <x v="1"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="1"/>
-    <x v="0"/>
-    <s v="筆"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="1"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="14"/>
+    <n v="8"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
-    <x v="1"/>
     <x v="0"/>
-    <s v="筆"/>
-    <x v="15"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="24"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
     <x v="1"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="16"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
     <x v="1"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="17"/>
-  </r>
-  <r>
+    <x v="1"/>
     <x v="0"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="筆"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="19"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="20"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="筆"/>
-    <x v="21"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="22"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="23"/>
+    <n v="11"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
+    <x v="1"/>
     <x v="2"/>
     <x v="0"/>
-    <s v="筆"/>
-    <x v="24"/>
+    <n v="7"/>
   </r>
   <r>
     <x v="2"/>
-    <n v="2021"/>
-    <x v="2"/>
     <x v="1"/>
-    <s v="萬元"/>
-    <x v="25"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="4"/>
   </r>
   <r>
-    <x v="2"/>
-    <n v="2021"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="26"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="95"/>
   </r>
   <r>
-    <x v="0"/>
-    <n v="2021"/>
     <x v="3"/>
     <x v="0"/>
-    <s v="筆"/>
-    <x v="27"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9"/>
   </r>
   <r>
+    <x v="3"/>
     <x v="0"/>
-    <n v="2021"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="2"/>
+  </r>
+  <r>
     <x v="3"/>
     <x v="1"/>
-    <s v="萬元"/>
-    <x v="28"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="50"/>
   </r>
   <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="2021"/>
-    <x v="3"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="29"/>
+    <n v="12"/>
   </r>
   <r>
+    <x v="3"/>
     <x v="1"/>
-    <n v="2021"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
     <x v="3"/>
     <x v="0"/>
-    <s v="筆"/>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="3"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="31"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2021"/>
-    <x v="3"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="2021"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="筆"/>
-    <x v="33"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="2021"/>
-    <x v="3"/>
-    <x v="1"/>
-    <s v="萬元"/>
-    <x v="34"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="2021"/>
-    <x v="3"/>
-    <x v="2"/>
-    <s v="萬元"/>
-    <x v="35"/>
+    <n v="3"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -10100,7 +14689,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="0"/>
+    <n v="303"/>
   </r>
   <r>
     <x v="1"/>
@@ -10108,7 +14697,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="1"/>
+    <n v="419"/>
   </r>
   <r>
     <x v="2"/>
@@ -10116,7 +14705,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="2"/>
+    <n v="22"/>
   </r>
   <r>
     <x v="3"/>
@@ -10124,7 +14713,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="3"/>
+    <n v="113"/>
   </r>
   <r>
     <x v="0"/>
@@ -10132,7 +14721,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="4"/>
+    <n v="0.35360000000000003"/>
   </r>
   <r>
     <x v="1"/>
@@ -10140,7 +14729,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="5"/>
+    <n v="0.4889"/>
   </r>
   <r>
     <x v="2"/>
@@ -10148,7 +14737,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="6"/>
+    <n v="2.5700000000000001E-2"/>
   </r>
   <r>
     <x v="3"/>
@@ -10156,7 +14745,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="7"/>
+    <n v="0.13189999999999999"/>
   </r>
   <r>
     <x v="0"/>
@@ -10164,7 +14753,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="8"/>
+    <n v="415"/>
   </r>
   <r>
     <x v="1"/>
@@ -10172,7 +14761,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="9"/>
+    <n v="442"/>
   </r>
   <r>
     <x v="2"/>
@@ -10180,7 +14769,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="10"/>
+    <n v="21"/>
   </r>
   <r>
     <x v="3"/>
@@ -10188,7 +14777,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="11"/>
+    <n v="33"/>
   </r>
   <r>
     <x v="0"/>
@@ -10196,7 +14785,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="12"/>
+    <n v="0.45550000000000002"/>
   </r>
   <r>
     <x v="1"/>
@@ -10204,7 +14793,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="13"/>
+    <n v="0.48520000000000002"/>
   </r>
   <r>
     <x v="2"/>
@@ -10212,7 +14801,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="14"/>
+    <n v="2.3099999999999999E-2"/>
   </r>
   <r>
     <x v="3"/>
@@ -10220,7 +14809,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="15"/>
+    <n v="3.6200000000000003E-2"/>
   </r>
   <r>
     <x v="0"/>
@@ -10228,7 +14817,7 @@
     <x v="2"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="16"/>
+    <n v="513"/>
   </r>
   <r>
     <x v="1"/>
@@ -10236,7 +14825,7 @@
     <x v="2"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="17"/>
+    <n v="492"/>
   </r>
   <r>
     <x v="2"/>
@@ -10244,7 +14833,7 @@
     <x v="2"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="18"/>
+    <n v="31"/>
   </r>
   <r>
     <x v="3"/>
@@ -10252,7 +14841,7 @@
     <x v="2"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="19"/>
+    <n v="28"/>
   </r>
   <r>
     <x v="0"/>
@@ -10260,7 +14849,7 @@
     <x v="2"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="20"/>
+    <n v="0.48209999999999997"/>
   </r>
   <r>
     <x v="1"/>
@@ -10268,7 +14857,7 @@
     <x v="2"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="21"/>
+    <n v="0.46239999999999998"/>
   </r>
   <r>
     <x v="2"/>
@@ -10276,7 +14865,7 @@
     <x v="2"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="22"/>
+    <n v="2.9100000000000001E-2"/>
   </r>
   <r>
     <x v="3"/>
@@ -10284,7 +14873,7 @@
     <x v="2"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="23"/>
+    <n v="2.63E-2"/>
   </r>
   <r>
     <x v="0"/>
@@ -10292,7 +14881,7 @@
     <x v="3"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="24"/>
+    <n v="330"/>
   </r>
   <r>
     <x v="1"/>
@@ -10300,7 +14889,7 @@
     <x v="3"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="25"/>
+    <n v="367"/>
   </r>
   <r>
     <x v="2"/>
@@ -10308,7 +14897,7 @@
     <x v="3"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="26"/>
+    <n v="26"/>
   </r>
   <r>
     <x v="3"/>
@@ -10316,7 +14905,7 @@
     <x v="3"/>
     <x v="0"/>
     <s v="戶數"/>
-    <x v="27"/>
+    <n v="161"/>
   </r>
   <r>
     <x v="0"/>
@@ -10324,7 +14913,7 @@
     <x v="3"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="28"/>
+    <n v="0.37330000000000002"/>
   </r>
   <r>
     <x v="1"/>
@@ -10332,7 +14921,7 @@
     <x v="3"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="29"/>
+    <n v="0.41520000000000001"/>
   </r>
   <r>
     <x v="2"/>
@@ -10340,7 +14929,7 @@
     <x v="3"/>
     <x v="1"/>
     <s v="%"/>
-    <x v="30"/>
+    <n v="2.9399999999999999E-2"/>
   </r>
   <r>
     <x v="3"/>
@@ -10348,13 +14937,759 @@
     <x v="3"/>
     <x v="1"/>
     <s v="%"/>
+    <n v="0.18210000000000001"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="36">
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="857"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="965"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="27.1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="64"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1328"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="39.4"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="404"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1359"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="35.299999999999997"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="911"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1008"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="26.7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="73"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1360"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="40.1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="317"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1275"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="1064"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1053"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="27.8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="51"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1382"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="41.2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="398"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1425"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="1174"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1048"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="29.1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="122"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1469"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="43.4"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="筆"/>
+    <n v="199"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="萬元"/>
+    <n v="1422"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2021"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="萬元"/>
+    <n v="38.9"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="1"/>
     <x v="31"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="36"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="38"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="38"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="39"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="40"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="41"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="42"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="43"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="44"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="45"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="47"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="48"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="49"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="50"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/10"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="51"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="52"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="53"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="54"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="2021/11"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="55"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C933CB77-500D-0846-837D-B8F9FA10D073}" name="樞紐分析表1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C933CB77-500D-0846-837D-B8F9FA10D073}" name="樞紐分析表1" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="J10:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -10384,47 +15719,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="37">
-        <item x="11"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="29"/>
-        <item x="8"/>
-        <item x="17"/>
-        <item x="26"/>
-        <item x="35"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="32"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="33"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="28"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="27"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="34"/>
-        <item x="25"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -10532,7 +15827,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE5E1FF5-8F93-5D4B-8D53-2FA9409BDAE8}" name="樞紐分析表3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE5E1FF5-8F93-5D4B-8D53-2FA9409BDAE8}" name="樞紐分析表3" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H83:M88" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -10562,47 +15857,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="37">
-        <item x="11"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="29"/>
-        <item x="8"/>
-        <item x="17"/>
-        <item x="26"/>
-        <item x="35"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="32"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="33"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="28"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="27"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="34"/>
-        <item x="25"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -10755,7 +16010,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACF04336-7B3D-A342-9990-49B490C95592}" name="樞紐分析表2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACF04336-7B3D-A342-9990-49B490C95592}" name="樞紐分析表2" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="I49:M55" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0">
@@ -10785,47 +16040,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="37">
-        <item x="11"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="29"/>
-        <item x="8"/>
-        <item x="17"/>
-        <item x="26"/>
-        <item x="35"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="32"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="33"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="28"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="27"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="34"/>
-        <item x="25"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="2"/>
@@ -10978,7 +16193,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D0F693C-7021-BC44-94FB-78B7F3E25852}" name="樞紐分析表4" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D0F693C-7021-BC44-94FB-78B7F3E25852}" name="樞紐分析表4" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="J37:O43" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0" sortType="descending">
@@ -11347,7 +16562,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E472707-6589-414B-B8AA-943FABDA29D1}" name="樞紐分析表5" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E472707-6589-414B-B8AA-943FABDA29D1}" name="樞紐分析表5" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="I76:J81" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -11369,43 +16584,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="33">
-        <item x="14"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="30"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="12"/>
-        <item x="21"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="26"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="27"/>
-        <item x="0"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -11490,6 +16669,866 @@
           </reference>
           <reference field="0" count="1" selected="0">
             <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{145E0A91-C704-EF45-B78E-5C89E5EB2381}" name="樞紐分析表7" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="I48:N54" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="57">
+        <item x="51"/>
+        <item x="36"/>
+        <item x="55"/>
+        <item x="26"/>
+        <item x="42"/>
+        <item x="49"/>
+        <item x="39"/>
+        <item x="47"/>
+        <item x="50"/>
+        <item x="30"/>
+        <item x="54"/>
+        <item x="46"/>
+        <item x="53"/>
+        <item x="43"/>
+        <item x="32"/>
+        <item x="38"/>
+        <item x="35"/>
+        <item x="45"/>
+        <item x="31"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="29"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="37"/>
+        <item x="44"/>
+        <item x="52"/>
+        <item x="48"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="25"/>
+        <item x="19"/>
+        <item x="24"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 數字" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="20">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D41697F-C9C1-2D4B-B5D2-FB3BE3127AE7}" name="樞紐分析表6" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="J10:O16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item m="1" x="4"/>
+        <item m="1" x="7"/>
+        <item m="1" x="6"/>
+        <item m="1" x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="1" hier="-1"/>
+    <pageField fld="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="加總 - 數字" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="24">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -11808,9 +17847,11 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13852,13 +19893,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA92196-98A7-9F43-9F6D-B6A0BC8691EE}">
-  <dimension ref="C3:G210"/>
+  <dimension ref="C3:O210"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="8" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:7">
+    <row r="3" spans="3:15">
       <c r="C3" t="s">
         <v>31</v>
       </c>
@@ -13866,7 +19921,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="3:7">
+    <row r="4" spans="3:15">
       <c r="C4" t="s">
         <v>33</v>
       </c>
@@ -13874,7 +19929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="3:7">
+    <row r="5" spans="3:15">
       <c r="C5" t="s">
         <v>34</v>
       </c>
@@ -13882,7 +19937,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="6" spans="3:7" ht="19">
+    <row r="6" spans="3:15" ht="19">
       <c r="C6" t="s">
         <v>37</v>
       </c>
@@ -13890,15 +19945,31 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="3:7">
+    <row r="7" spans="3:15">
+      <c r="J7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="3:15">
+      <c r="J8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15">
       <c r="C10" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -13906,16 +19977,22 @@
       <c r="G10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="3:7">
+      <c r="J10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15">
       <c r="C11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
         <v>48</v>
@@ -13923,16 +20000,34 @@
       <c r="G11">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="3:7">
+      <c r="J11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N11" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15">
       <c r="C12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F12" t="s">
         <v>48</v>
@@ -13940,16 +20035,34 @@
       <c r="G12">
         <v>142</v>
       </c>
-    </row>
-    <row r="13" spans="3:7">
+      <c r="J12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="6">
+        <v>63</v>
+      </c>
+      <c r="L12" s="6">
+        <v>48</v>
+      </c>
+      <c r="M12" s="6">
+        <v>145</v>
+      </c>
+      <c r="N12" s="6">
+        <v>73</v>
+      </c>
+      <c r="O12" s="6">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15">
       <c r="C13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>48</v>
@@ -13957,16 +20070,34 @@
       <c r="G13">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="3:7">
+      <c r="J13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="6">
+        <v>52</v>
+      </c>
+      <c r="L13" s="6">
+        <v>26</v>
+      </c>
+      <c r="M13" s="6">
+        <v>21</v>
+      </c>
+      <c r="N13" s="6">
+        <v>263</v>
+      </c>
+      <c r="O13" s="6">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15">
       <c r="C14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>48</v>
@@ -13974,16 +20105,34 @@
       <c r="G14">
         <v>187</v>
       </c>
-    </row>
-    <row r="15" spans="3:7">
+      <c r="J14" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="6">
+        <v>15</v>
+      </c>
+      <c r="L14" s="6">
+        <v>30</v>
+      </c>
+      <c r="M14" s="6">
+        <v>21</v>
+      </c>
+      <c r="N14" s="6">
+        <v>228</v>
+      </c>
+      <c r="O14" s="6">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15">
       <c r="C15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
         <v>48</v>
@@ -13991,16 +20140,34 @@
       <c r="G15">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="3:7">
+      <c r="J15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="6">
+        <v>28</v>
+      </c>
+      <c r="L15" s="6">
+        <v>5</v>
+      </c>
+      <c r="M15" s="6">
+        <v>5</v>
+      </c>
+      <c r="N15" s="6">
+        <v>400</v>
+      </c>
+      <c r="O15" s="6">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15">
       <c r="C16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
         <v>48</v>
@@ -14008,16 +20175,34 @@
       <c r="G16">
         <v>121</v>
       </c>
+      <c r="J16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="6">
+        <v>158</v>
+      </c>
+      <c r="L16" s="6">
+        <v>109</v>
+      </c>
+      <c r="M16" s="6">
+        <v>192</v>
+      </c>
+      <c r="N16" s="6">
+        <v>964</v>
+      </c>
+      <c r="O16" s="6">
+        <v>1423</v>
+      </c>
     </row>
     <row r="17" spans="3:7">
       <c r="C17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s">
         <v>48</v>
@@ -14028,13 +20213,13 @@
     </row>
     <row r="18" spans="3:7">
       <c r="C18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
         <v>48</v>
@@ -14048,10 +20233,10 @@
         <v>72</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
         <v>48</v>
@@ -14065,10 +20250,10 @@
         <v>72</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
         <v>48</v>
@@ -14082,10 +20267,10 @@
         <v>72</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
         <v>48</v>
@@ -14099,10 +20284,10 @@
         <v>72</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s">
         <v>48</v>
@@ -14116,10 +20301,10 @@
         <v>72</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
         <v>48</v>
@@ -14133,10 +20318,10 @@
         <v>72</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F24" t="s">
         <v>48</v>
@@ -14150,10 +20335,10 @@
         <v>72</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -14167,10 +20352,10 @@
         <v>72</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
         <v>48</v>
@@ -14181,13 +20366,13 @@
     </row>
     <row r="27" spans="3:7">
       <c r="C27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
         <v>48</v>
@@ -14198,13 +20383,13 @@
     </row>
     <row r="28" spans="3:7">
       <c r="C28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s">
         <v>48</v>
@@ -14215,13 +20400,13 @@
     </row>
     <row r="29" spans="3:7">
       <c r="C29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>48</v>
@@ -14232,13 +20417,13 @@
     </row>
     <row r="30" spans="3:7">
       <c r="C30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s">
         <v>48</v>
@@ -14249,13 +20434,13 @@
     </row>
     <row r="31" spans="3:7">
       <c r="C31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
         <v>48</v>
@@ -14266,13 +20451,13 @@
     </row>
     <row r="32" spans="3:7">
       <c r="C32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
         <v>48</v>
@@ -14281,15 +20466,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="3:7">
+    <row r="33" spans="3:10">
       <c r="C33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
         <v>48</v>
@@ -14298,15 +20483,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="3:7">
+    <row r="34" spans="3:10">
       <c r="C34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s">
         <v>48</v>
@@ -14315,15 +20500,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="3:7">
+    <row r="35" spans="3:10">
       <c r="C35" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
         <v>48</v>
@@ -14332,15 +20517,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="3:7">
+    <row r="36" spans="3:10">
       <c r="C36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s">
         <v>48</v>
@@ -14349,15 +20534,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="3:7">
+    <row r="37" spans="3:10">
       <c r="C37" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -14366,15 +20551,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="3:7">
+    <row r="38" spans="3:10">
       <c r="C38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F38" t="s">
         <v>48</v>
@@ -14383,15 +20568,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="3:7">
+    <row r="39" spans="3:10">
       <c r="C39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F39" t="s">
         <v>48</v>
@@ -14400,15 +20585,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="3:7">
+    <row r="40" spans="3:10">
       <c r="C40" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s">
         <v>48</v>
@@ -14417,15 +20602,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="3:7">
+    <row r="41" spans="3:10">
       <c r="C41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F41" t="s">
         <v>48</v>
@@ -14434,15 +20619,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="3:7">
+    <row r="42" spans="3:10">
       <c r="C42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E42" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
         <v>48</v>
@@ -14451,118 +20636,686 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="3:7">
-      <c r="D43" s="12"/>
-    </row>
-    <row r="44" spans="3:7">
-      <c r="D44" s="12"/>
-    </row>
-    <row r="45" spans="3:7">
-      <c r="D45" s="12"/>
-    </row>
-    <row r="46" spans="3:7">
-      <c r="D46" s="12"/>
-    </row>
-    <row r="47" spans="3:7">
-      <c r="D47" s="12"/>
-    </row>
-    <row r="48" spans="3:7">
-      <c r="D48" s="12"/>
-    </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="12"/>
-    </row>
-    <row r="50" spans="4:4">
-      <c r="D50" s="12"/>
-    </row>
-    <row r="51" spans="4:4">
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="12"/>
-    </row>
-    <row r="53" spans="4:4">
-      <c r="D53" s="12"/>
-    </row>
-    <row r="54" spans="4:4">
-      <c r="D54" s="12"/>
-    </row>
-    <row r="55" spans="4:4">
-      <c r="D55" s="12"/>
-    </row>
-    <row r="56" spans="4:4">
-      <c r="D56" s="12"/>
-    </row>
-    <row r="57" spans="4:4">
-      <c r="D57" s="12"/>
-    </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="12"/>
-    </row>
-    <row r="59" spans="4:4">
-      <c r="D59" s="12"/>
-    </row>
-    <row r="60" spans="4:4">
-      <c r="D60" s="12"/>
-    </row>
-    <row r="61" spans="4:4">
-      <c r="D61" s="12"/>
-    </row>
-    <row r="62" spans="4:4">
-      <c r="D62" s="12"/>
-    </row>
-    <row r="63" spans="4:4">
-      <c r="D63" s="12"/>
-    </row>
-    <row r="64" spans="4:4">
-      <c r="D64" s="12"/>
-    </row>
-    <row r="65" spans="4:4">
-      <c r="D65" s="12"/>
-    </row>
-    <row r="66" spans="4:4">
-      <c r="D66" s="12"/>
-    </row>
-    <row r="67" spans="4:4">
-      <c r="D67" s="12"/>
-    </row>
-    <row r="68" spans="4:4">
-      <c r="D68" s="12"/>
-    </row>
-    <row r="69" spans="4:4">
-      <c r="D69" s="12"/>
-    </row>
-    <row r="70" spans="4:4">
-      <c r="D70" s="12"/>
-    </row>
-    <row r="71" spans="4:4">
-      <c r="D71" s="12"/>
-    </row>
-    <row r="72" spans="4:4">
-      <c r="D72" s="12"/>
-    </row>
-    <row r="73" spans="4:4">
-      <c r="D73" s="12"/>
-    </row>
-    <row r="74" spans="4:4">
-      <c r="D74" s="12"/>
-    </row>
-    <row r="75" spans="4:4">
+    <row r="43" spans="3:10">
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43" s="9">
+        <v>5.6300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10">
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0.29580000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10">
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0.25829999999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10">
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0.3896</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10">
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E47" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" t="s">
+        <v>57</v>
+      </c>
+      <c r="G47" s="9">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10">
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" t="s">
+        <v>57</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14">
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" t="s">
+        <v>78</v>
+      </c>
+      <c r="F49" t="s">
+        <v>57</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0.21490000000000001</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J49" t="s">
+        <v>73</v>
+      </c>
+      <c r="K49" t="s">
+        <v>71</v>
+      </c>
+      <c r="L49" t="s">
+        <v>75</v>
+      </c>
+      <c r="M49" t="s">
+        <v>67</v>
+      </c>
+      <c r="N49" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14">
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0.44009999999999999</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0.43254999999999999</v>
+      </c>
+      <c r="K50" s="9">
+        <v>0.442</v>
+      </c>
+      <c r="L50" s="9">
+        <v>0.73934999999999995</v>
+      </c>
+      <c r="M50" s="9">
+        <v>7.5649999999999995E-2</v>
+      </c>
+      <c r="N50" s="9">
+        <v>0.42238750000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14">
+      <c r="C51" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0.43659999999999999</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J51" s="9">
+        <v>0.30359999999999998</v>
+      </c>
+      <c r="K51" s="9">
+        <v>0.23810000000000001</v>
+      </c>
+      <c r="L51" s="9">
+        <v>0.11845</v>
+      </c>
+      <c r="M51" s="9">
+        <v>0.27290000000000003</v>
+      </c>
+      <c r="N51" s="9">
+        <v>0.23326249999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14">
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F52" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0.2394</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0.1132</v>
+      </c>
+      <c r="K52" s="9">
+        <v>0.26629999999999998</v>
+      </c>
+      <c r="L52" s="9">
+        <v>0.11365</v>
+      </c>
+      <c r="M52" s="9">
+        <v>0.23659999999999998</v>
+      </c>
+      <c r="N52" s="9">
+        <v>0.1824375</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14">
+      <c r="C53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" t="s">
+        <v>57</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0.29580000000000001</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J53" s="9">
+        <v>0.15065000000000001</v>
+      </c>
+      <c r="K53" s="9">
+        <v>5.355E-2</v>
+      </c>
+      <c r="L53" s="9">
+        <v>2.8549999999999999E-2</v>
+      </c>
+      <c r="M53" s="9">
+        <v>0.41485</v>
+      </c>
+      <c r="N53" s="9">
+        <v>0.16189999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14">
+      <c r="C54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" t="s">
+        <v>57</v>
+      </c>
+      <c r="G54" s="9">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" s="9">
+        <v>0.24999999999999997</v>
+      </c>
+      <c r="K54" s="9">
+        <v>0.2499875</v>
+      </c>
+      <c r="L54" s="9">
+        <v>0.24999999999999997</v>
+      </c>
+      <c r="M54" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N54" s="9">
+        <v>0.24999687500000001</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14">
+      <c r="C55" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>80</v>
+      </c>
+      <c r="F55" t="s">
+        <v>57</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0.44740000000000002</v>
+      </c>
+    </row>
+    <row r="56" spans="3:14">
+      <c r="C56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" t="s">
+        <v>82</v>
+      </c>
+      <c r="F56" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0.23680000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="3:14">
+      <c r="C57" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57" t="s">
+        <v>57</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0.23680000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14">
+      <c r="C58" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" t="s">
+        <v>84</v>
+      </c>
+      <c r="F58" t="s">
+        <v>57</v>
+      </c>
+      <c r="G58" s="9">
+        <v>7.8899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14">
+      <c r="C59" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59" t="s">
+        <v>57</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0.35399999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14">
+      <c r="C60" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" t="s">
+        <v>82</v>
+      </c>
+      <c r="F60" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0.36280000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14">
+      <c r="C61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="9">
+        <v>7.0800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14">
+      <c r="C62" t="s">
+        <v>74</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" t="s">
+        <v>57</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0.21240000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14">
+      <c r="C63" t="s">
+        <v>74</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63" t="s">
+        <v>80</v>
+      </c>
+      <c r="F63" t="s">
+        <v>57</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0.5111</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14">
+      <c r="C64" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E64" t="s">
+        <v>82</v>
+      </c>
+      <c r="F64" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0.24440000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="3:7">
+      <c r="C65" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E65" t="s">
+        <v>78</v>
+      </c>
+      <c r="F65" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0.15559999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7">
+      <c r="C66" t="s">
+        <v>74</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E66" t="s">
+        <v>84</v>
+      </c>
+      <c r="F66" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="9">
+        <v>8.8900000000000007E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7">
+      <c r="C67" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" t="s">
+        <v>80</v>
+      </c>
+      <c r="F67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0.81200000000000006</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7">
+      <c r="C68" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" s="9">
+        <v>7.6899999999999996E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="3:7">
+      <c r="C69" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" t="s">
+        <v>78</v>
+      </c>
+      <c r="F69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" s="9">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="3:7">
+      <c r="C70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" t="s">
+        <v>84</v>
+      </c>
+      <c r="F70" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" s="9">
+        <v>1.7100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="3:7">
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E71" t="s">
+        <v>80</v>
+      </c>
+      <c r="F71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0.66669999999999996</v>
+      </c>
+    </row>
+    <row r="72" spans="3:7">
+      <c r="C72" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E72" t="s">
+        <v>82</v>
+      </c>
+      <c r="F72" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" s="9">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="73" spans="3:7">
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E73" t="s">
+        <v>78</v>
+      </c>
+      <c r="F73" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="9">
+        <v>0.1333</v>
+      </c>
+    </row>
+    <row r="74" spans="3:7">
+      <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E74" t="s">
+        <v>84</v>
+      </c>
+      <c r="F74" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="75" spans="3:7">
       <c r="D75" s="12"/>
     </row>
-    <row r="76" spans="4:4">
+    <row r="76" spans="3:7">
       <c r="D76" s="12"/>
     </row>
-    <row r="77" spans="4:4">
+    <row r="77" spans="3:7">
       <c r="D77" s="12"/>
     </row>
-    <row r="78" spans="4:4">
+    <row r="78" spans="3:7">
       <c r="D78" s="12"/>
     </row>
-    <row r="79" spans="4:4">
+    <row r="79" spans="3:7">
       <c r="D79" s="12"/>
     </row>
-    <row r="80" spans="4:4">
+    <row r="80" spans="3:7">
       <c r="D80" s="12"/>
     </row>
     <row r="81" spans="4:4">
@@ -14958,5 +21711,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>